--- a/Packages/cn.etetet.childrenmgr/Luban/Config/Base/__tables__.xlsx
+++ b/Packages/cn.etetet.childrenmgr/Luban/Config/Base/__tables__.xlsx
@@ -1226,8 +1226,8 @@
         <v>32</v>
       </c>
       <c r="D5" t="str">
-        <f>_xlfn.CONCAT("cn.etetet.",B5,".",C5,"ConfigCategory")</f>
-        <v>cn.etetet.childrenmgr.SchoolGradeConfigCategory</v>
+        <f>_xlfn.CONCAT("cn.etetet.",B5,".SchoolGrade.",C5,"ConfigCategory")</f>
+        <v>cn.etetet.childrenmgr.SchoolGrade.SchoolGradeConfigCategory</v>
       </c>
       <c r="E5" t="str">
         <f>_xlfn.CONCAT(C5,"Config")</f>
@@ -1253,8 +1253,8 @@
         <v>33</v>
       </c>
       <c r="D6" t="str">
-        <f>_xlfn.CONCAT("cn.etetet.",B6,".",C6,"ConfigCategory")</f>
-        <v>cn.etetet.childrenmgr.GradeClassConfigCategory</v>
+        <f>_xlfn.CONCAT("cn.etetet.",B6,".SchoolGrade.",C6,"ConfigCategory")</f>
+        <v>cn.etetet.childrenmgr.SchoolGrade.GradeClassConfigCategory</v>
       </c>
       <c r="E6" t="str">
         <f>_xlfn.CONCAT(C6,"Config")</f>
@@ -1264,8 +1264,8 @@
         <v>1</v>
       </c>
       <c r="G6" t="str">
-        <f>_xlfn.CONCAT("..\..\..\..\cn.etetet.",B6,"\Luban\Config\Datas\GradeClass\",C6,".xlsx")</f>
-        <v>..\..\..\..\cn.etetet.childrenmgr\Luban\Config\Datas\GradeClass\GradeClass.xlsx</v>
+        <f>_xlfn.CONCAT("..\..\..\..\cn.etetet.",B6,"\Luban\Config\Datas\SchoolGrade\",C6,".xlsx")</f>
+        <v>..\..\..\..\cn.etetet.childrenmgr\Luban\Config\Datas\SchoolGrade\GradeClass.xlsx</v>
       </c>
       <c r="M6" t="str">
         <f>_xlfn.CONCAT(C6,"ConfigCategory")</f>
